--- a/Indonesia Trade 2019-2024 EDA.xlsx
+++ b/Indonesia Trade 2019-2024 EDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Os 11\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C11096-7A32-40A3-86F6-BA58A75B5933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85BB7C25-B1B4-4E59-A23D-7A05B9DF0E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="537" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="537" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4211" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4209" uniqueCount="554">
   <si>
     <t>INDONESIAN TRADE FLOW ANALYSIS
 Exploratory Data Analysis  ·  FY2019–2024</t>
@@ -1158,9 +1158,6 @@
     <t>IDN-0264</t>
   </si>
   <si>
-    <t>STEP 1 · DATA PROFILE — Inspect Before You Analyse</t>
-  </si>
-  <si>
     <t>Data profiling reveals the shape, completeness, and distribution of your dataset before any analysis begins.</t>
   </si>
   <si>
@@ -1344,9 +1341,6 @@
     <t>Imports</t>
   </si>
   <si>
-    <t>💡 ANALYST NOTE: No missing values in this dataset. In real-world trade data (BPS/UN Comtrade), expect 5–15% gaps due to reporting delays, confidential shipments, or rounding suppression.</t>
-  </si>
-  <si>
     <t>STEP 2 · UNIVARIATE ANALYSIS — One Variable at a Time</t>
   </si>
   <si>
@@ -1596,9 +1590,6 @@
     <t>STEP 6 · KEY FINDINGS &amp; ANALYTICAL INSIGHTS</t>
   </si>
   <si>
-    <t>Synthesised conclusions drawn from the EDA. These findings form the basis of the written case study.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  FINDING 1  ·  COMMODITY CONCENTRATION RISK</t>
   </si>
   <si>
@@ -1717,6 +1708,9 @@
   </si>
   <si>
     <t>This workbook conducts a structured Exploratory Data Analysis (EDA) on Indonesia's international trade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEP 1 · DATA PROFILE </t>
   </si>
 </sst>
 </file>
@@ -2181,7 +2175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2398,157 +2392,50 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="32" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2569,52 +2456,160 @@
     <xf numFmtId="165" fontId="33" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2846,7 +2841,7 @@
             <c:numRef>
               <c:f>[1]DASHBOARD!$B$10:$B$15</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>47442</c:v>
@@ -2966,7 +2961,7 @@
             <c:numRef>
               <c:f>[1]DASHBOARD!$C$10:$C$15</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>41620</c:v>
@@ -3133,7 +3128,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3382,7 +3377,7 @@
             <c:numRef>
               <c:f>[1]DASHBOARD!$F$10:$F$21</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>88270</c:v>
@@ -3537,7 +3532,7 @@
             <c:numRef>
               <c:f>[1]DASHBOARD!$G$10:$G$21</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -3688,7 +3683,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3918,7 +3913,7 @@
             <c:numRef>
               <c:f>[1]DASHBOARD!$N$10:$N$15</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>4880</c:v>
@@ -4093,7 +4088,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4336,7 +4331,7 @@
             <c:numRef>
               <c:f>[1]DASHBOARD!$J$10:$J$19</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>166040</c:v>
@@ -4479,7 +4474,7 @@
             <c:numRef>
               <c:f>[1]DASHBOARD!$K$10:$K$19</c:f>
               <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>101860</c:v>
@@ -4624,7 +4619,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -10371,147 +10366,147 @@
     <row r="1" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="103"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="103"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
     </row>
     <row r="4" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="2:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="86" t="s">
-        <v>535</v>
-      </c>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
+      <c r="B5" s="105" t="s">
+        <v>532</v>
+      </c>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
     </row>
     <row r="6" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
     </row>
     <row r="8" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="83" t="s">
-        <v>555</v>
-      </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
+      <c r="B8" s="107" t="s">
+        <v>552</v>
+      </c>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="107"/>
+      <c r="J8" s="107"/>
     </row>
     <row r="9" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="83"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="107"/>
     </row>
     <row r="10" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="83"/>
+      <c r="C10" s="107"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="107"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="107"/>
+      <c r="I10" s="107"/>
+      <c r="J10" s="107"/>
     </row>
     <row r="11" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="107"/>
     </row>
     <row r="12" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="107"/>
+      <c r="I12" s="107"/>
+      <c r="J12" s="107"/>
     </row>
     <row r="13" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="83" t="s">
-        <v>554</v>
-      </c>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
+      <c r="B13" s="107" t="s">
+        <v>551</v>
+      </c>
+      <c r="C13" s="107"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="107"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="107"/>
     </row>
     <row r="14" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="82" t="s">
+      <c r="B15" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="82"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="82"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="108"/>
+      <c r="G15" s="108"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="108"/>
+      <c r="J15" s="108"/>
     </row>
     <row r="16" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
@@ -10529,194 +10524,194 @@
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="C17" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="77"/>
-      <c r="E17" s="78" t="s">
+      <c r="D17" s="109"/>
+      <c r="E17" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
     </row>
     <row r="18" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="111" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="80"/>
-      <c r="E18" s="81" t="s">
+      <c r="D18" s="111"/>
+      <c r="E18" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="81"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="112"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
     </row>
     <row r="19" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="75" t="s">
+      <c r="C19" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="75"/>
-      <c r="E19" s="76" t="s">
+      <c r="D19" s="113"/>
+      <c r="E19" s="114" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="76"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="114"/>
+      <c r="I19" s="114"/>
     </row>
     <row r="20" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="77" t="s">
+      <c r="C20" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="77"/>
-      <c r="E20" s="78" t="s">
+      <c r="D20" s="109"/>
+      <c r="E20" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
     </row>
     <row r="21" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="80" t="s">
+      <c r="C21" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="80"/>
-      <c r="E21" s="81" t="s">
+      <c r="D21" s="111"/>
+      <c r="E21" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="81"/>
-      <c r="G21" s="81"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
     </row>
     <row r="22" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="75" t="s">
+      <c r="C22" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="75"/>
-      <c r="E22" s="76" t="s">
+      <c r="D22" s="113"/>
+      <c r="E22" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
+      <c r="F22" s="114"/>
+      <c r="G22" s="114"/>
+      <c r="H22" s="114"/>
+      <c r="I22" s="114"/>
     </row>
     <row r="23" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="77" t="s">
+      <c r="C23" s="109" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="77"/>
-      <c r="E23" s="78" t="s">
+      <c r="D23" s="109"/>
+      <c r="E23" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
     </row>
     <row r="24" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="79" t="s">
+      <c r="B26" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
-      <c r="I26" s="79"/>
-      <c r="J26" s="79"/>
+      <c r="C26" s="115"/>
+      <c r="D26" s="115"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="115"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="115"/>
+      <c r="J26" s="115"/>
     </row>
     <row r="27" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="74" t="s">
+      <c r="B27" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="74"/>
+      <c r="C27" s="116"/>
       <c r="D27" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="74" t="s">
+      <c r="E27" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="74"/>
+      <c r="F27" s="116"/>
       <c r="G27" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H27" s="74" t="s">
+      <c r="H27" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="I27" s="74"/>
+      <c r="I27" s="116"/>
       <c r="J27" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="74" t="s">
+      <c r="B28" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="74"/>
+      <c r="C28" s="116"/>
       <c r="D28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E28" s="74" t="s">
+      <c r="E28" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="F28" s="74"/>
+      <c r="F28" s="116"/>
       <c r="G28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="74" t="s">
+      <c r="H28" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="I28" s="74"/>
+      <c r="I28" s="116"/>
       <c r="J28" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="29" spans="2:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="74" t="s">
+      <c r="B29" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="74"/>
+      <c r="C29" s="116"/>
       <c r="D29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="74" t="s">
+      <c r="E29" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="74"/>
+      <c r="F29" s="116"/>
       <c r="G29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H29" s="74" t="s">
+      <c r="H29" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="I29" s="74"/>
+      <c r="I29" s="116"/>
       <c r="J29" s="6" t="s">
         <v>22</v>
       </c>
@@ -10736,32 +10731,6 @@
     <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B10:J10"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:I18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:I19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:I20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:I21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:I22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:I23"/>
-    <mergeCell ref="B26:J26"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="H29:I29"/>
@@ -10771,6 +10740,32 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="H28:I28"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:I22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:I23"/>
+    <mergeCell ref="B26:J26"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:I19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:I21"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:I18"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B8:J8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -20168,579 +20163,579 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="96" t="s">
+        <v>533</v>
+      </c>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+    </row>
+    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="97" t="s">
+        <v>534</v>
+      </c>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+    </row>
+    <row r="4" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="98" t="s">
+        <v>535</v>
+      </c>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="99" t="s">
         <v>536</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-    </row>
-    <row r="2" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="89" t="s">
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="100" t="s">
         <v>537</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89"/>
-      <c r="T2" s="89"/>
-    </row>
-    <row r="4" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="120" t="s">
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="101" t="s">
         <v>538</v>
       </c>
-      <c r="B4" s="120"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="121" t="s">
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="102" t="s">
         <v>539</v>
       </c>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="122" t="s">
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="99" t="s">
         <v>540</v>
       </c>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="123" t="s">
-        <v>541</v>
-      </c>
-      <c r="K4" s="123"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="124" t="s">
-        <v>542</v>
-      </c>
-      <c r="N4" s="124"/>
-      <c r="O4" s="124"/>
-      <c r="P4" s="121" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q4" s="121"/>
-      <c r="R4" s="121"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="99"/>
     </row>
     <row r="5" spans="1:20" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="125">
+      <c r="A5" s="90">
         <f>SUMIF([1]DATA_TABLE!C2:C265,"Export",[1]DATA_TABLE!H2:H265)</f>
         <v>379518</v>
       </c>
-      <c r="B5" s="125"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="126">
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="91">
         <f>SUMIF([1]DATA_TABLE!C2:C265,"Import",[1]DATA_TABLE!H2:H265)</f>
         <v>273070</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="127">
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="92">
         <f>SUMIF([1]DATA_TABLE!C2:C265,"Export",[1]DATA_TABLE!H2:H265)-SUMIF([1]DATA_TABLE!C2:C265,"Import",[1]DATA_TABLE!H2:H265)</f>
         <v>106448</v>
       </c>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="128" t="s">
-        <v>544</v>
-      </c>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="129" t="s">
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="93" t="s">
+        <v>541</v>
+      </c>
+      <c r="K5" s="93"/>
+      <c r="L5" s="93"/>
+      <c r="M5" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="N5" s="129"/>
-      <c r="O5" s="129"/>
-      <c r="P5" s="130">
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="95">
         <f>IFERROR((SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,"Nickel Products",[1]DATA_TABLE!B2:B265,2024)/SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,"Nickel Products",[1]DATA_TABLE!B2:B265,2019))^(1/5)-1,0)</f>
         <v>0.36340169584631954</v>
       </c>
-      <c r="Q5" s="130"/>
-      <c r="R5" s="130"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="95"/>
     </row>
     <row r="6" spans="1:20" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="131" t="s">
+      <c r="A6" s="85" t="s">
+        <v>542</v>
+      </c>
+      <c r="B6" s="85"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="86" t="s">
+        <v>542</v>
+      </c>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="87" t="s">
+        <v>542</v>
+      </c>
+      <c r="H6" s="87"/>
+      <c r="I6" s="87"/>
+      <c r="J6" s="88" t="s">
+        <v>543</v>
+      </c>
+      <c r="K6" s="88"/>
+      <c r="L6" s="88"/>
+      <c r="M6" s="89" t="s">
+        <v>544</v>
+      </c>
+      <c r="N6" s="89"/>
+      <c r="O6" s="89"/>
+      <c r="P6" s="86" t="s">
         <v>545</v>
       </c>
-      <c r="B6" s="131"/>
-      <c r="C6" s="131"/>
-      <c r="D6" s="132" t="s">
-        <v>545</v>
-      </c>
-      <c r="E6" s="132"/>
-      <c r="F6" s="132"/>
-      <c r="G6" s="133" t="s">
-        <v>545</v>
-      </c>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="134" t="s">
+      <c r="Q6" s="86"/>
+      <c r="R6" s="86"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="81" t="s">
         <v>546</v>
       </c>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
-      <c r="M6" s="135" t="s">
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="E8" s="82" t="s">
         <v>547</v>
       </c>
-      <c r="N6" s="135"/>
-      <c r="O6" s="135"/>
-      <c r="P6" s="132" t="s">
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="I8" s="83" t="s">
         <v>548</v>
       </c>
-      <c r="Q6" s="132"/>
-      <c r="R6" s="132"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="136" t="s">
+      <c r="J8" s="83"/>
+      <c r="K8" s="83"/>
+      <c r="M8" s="84" t="s">
         <v>549</v>
       </c>
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="E8" s="137" t="s">
-        <v>550</v>
-      </c>
-      <c r="F8" s="137"/>
-      <c r="G8" s="137"/>
-      <c r="I8" s="138" t="s">
-        <v>551</v>
-      </c>
-      <c r="J8" s="138"/>
-      <c r="K8" s="138"/>
-      <c r="M8" s="139" t="s">
-        <v>552</v>
-      </c>
-      <c r="N8" s="139"/>
+      <c r="N8" s="84"/>
     </row>
     <row r="9" spans="1:20" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A9" s="44" t="s">
         <v>48</v>
       </c>
       <c r="B9" s="44" t="s">
+        <v>428</v>
+      </c>
+      <c r="C9" s="44" t="s">
         <v>429</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>430</v>
       </c>
       <c r="E9" s="44" t="s">
         <v>50</v>
       </c>
       <c r="F9" s="44" t="s">
+        <v>428</v>
+      </c>
+      <c r="G9" s="44" t="s">
         <v>429</v>
       </c>
-      <c r="G9" s="44" t="s">
-        <v>430</v>
-      </c>
-      <c r="I9" s="140" t="s">
-        <v>442</v>
-      </c>
-      <c r="J9" s="140" t="s">
+      <c r="I9" s="74" t="s">
+        <v>440</v>
+      </c>
+      <c r="J9" s="74" t="s">
+        <v>428</v>
+      </c>
+      <c r="K9" s="74" t="s">
         <v>429</v>
       </c>
-      <c r="K9" s="140" t="s">
-        <v>430</v>
-      </c>
-      <c r="M9" s="141" t="s">
+      <c r="M9" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="N9" s="141" t="s">
-        <v>553</v>
+      <c r="N9" s="75" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="142">
+      <c r="A10" s="76">
         <v>2019</v>
       </c>
-      <c r="B10" s="143">
+      <c r="B10" s="77">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Export",[1]DATA_TABLE!B2:B265,A10)</f>
         <v>47442</v>
       </c>
-      <c r="C10" s="144">
+      <c r="C10" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Import",[1]DATA_TABLE!B2:B265,A10)</f>
         <v>41620</v>
       </c>
-      <c r="E10" s="145" t="s">
+      <c r="E10" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="146">
+      <c r="F10" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E10,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>88270</v>
       </c>
-      <c r="G10" s="146">
+      <c r="G10" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E10,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="145" t="s">
+      <c r="I10" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="J10" s="146">
+      <c r="J10" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I10,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>166040</v>
       </c>
-      <c r="K10" s="146">
+      <c r="K10" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I10,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>101860</v>
       </c>
-      <c r="M10" s="142">
+      <c r="M10" s="76">
         <v>2019</v>
       </c>
-      <c r="N10" s="144">
+      <c r="N10" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,"Nickel Products",[1]DATA_TABLE!B2:B265,M10)</f>
         <v>4880</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="142">
+      <c r="A11" s="76">
         <v>2020</v>
       </c>
-      <c r="B11" s="143">
+      <c r="B11" s="77">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Export",[1]DATA_TABLE!B2:B265,A11)</f>
         <v>37208</v>
       </c>
-      <c r="C11" s="144">
+      <c r="C11" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Import",[1]DATA_TABLE!B2:B265,A11)</f>
         <v>32570</v>
       </c>
-      <c r="E11" s="145" t="s">
+      <c r="E11" s="79" t="s">
         <v>101</v>
       </c>
-      <c r="F11" s="146">
+      <c r="F11" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E11,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>148610</v>
       </c>
-      <c r="G11" s="146">
+      <c r="G11" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E11,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="145" t="s">
+      <c r="I11" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="146">
+      <c r="J11" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I11,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>66950</v>
       </c>
-      <c r="K11" s="146">
+      <c r="K11" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I11,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>0</v>
       </c>
-      <c r="M11" s="142">
+      <c r="M11" s="76">
         <v>2020</v>
       </c>
-      <c r="N11" s="144">
+      <c r="N11" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,"Nickel Products",[1]DATA_TABLE!B2:B265,M11)</f>
         <v>5790</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="142">
+      <c r="A12" s="76">
         <v>2021</v>
       </c>
-      <c r="B12" s="143">
+      <c r="B12" s="77">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Export",[1]DATA_TABLE!B2:B265,A12)</f>
         <v>57636</v>
       </c>
-      <c r="C12" s="144">
+      <c r="C12" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Import",[1]DATA_TABLE!B2:B265,A12)</f>
         <v>43060</v>
       </c>
-      <c r="E12" s="145" t="s">
+      <c r="E12" s="79" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="146">
+      <c r="F12" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E12,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>79130</v>
       </c>
-      <c r="G12" s="146">
+      <c r="G12" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E12,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="145" t="s">
+      <c r="I12" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="J12" s="146">
+      <c r="J12" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I12,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>53254</v>
       </c>
-      <c r="K12" s="146">
+      <c r="K12" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I12,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>35760</v>
       </c>
-      <c r="M12" s="142">
+      <c r="M12" s="76">
         <v>2021</v>
       </c>
-      <c r="N12" s="144">
+      <c r="N12" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,"Nickel Products",[1]DATA_TABLE!B2:B265,M12)</f>
         <v>9220</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="142">
+      <c r="A13" s="76">
         <v>2022</v>
       </c>
-      <c r="B13" s="143">
+      <c r="B13" s="77">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Export",[1]DATA_TABLE!B2:B265,A13)</f>
         <v>86916</v>
       </c>
-      <c r="C13" s="144">
+      <c r="C13" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Import",[1]DATA_TABLE!B2:B265,A13)</f>
         <v>53770</v>
       </c>
-      <c r="E13" s="145" t="s">
+      <c r="E13" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="F13" s="146">
+      <c r="F13" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E13,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>20330</v>
       </c>
-      <c r="G13" s="146">
+      <c r="G13" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E13,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>0</v>
       </c>
-      <c r="I13" s="145" t="s">
+      <c r="I13" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I13,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>10520</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I13,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>50520</v>
       </c>
-      <c r="M13" s="142">
+      <c r="M13" s="76">
         <v>2022</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,"Nickel Products",[1]DATA_TABLE!B2:B265,M13)</f>
         <v>15270</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="142">
+      <c r="A14" s="76">
         <v>2023</v>
       </c>
-      <c r="B14" s="143">
+      <c r="B14" s="77">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Export",[1]DATA_TABLE!B2:B265,A14)</f>
         <v>75926</v>
       </c>
-      <c r="C14" s="144">
+      <c r="C14" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Import",[1]DATA_TABLE!B2:B265,A14)</f>
         <v>48540</v>
       </c>
-      <c r="E14" s="145" t="s">
+      <c r="E14" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="F14" s="146">
+      <c r="F14" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E14,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>37720</v>
       </c>
-      <c r="G14" s="146">
+      <c r="G14" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E14,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>0</v>
       </c>
-      <c r="I14" s="145" t="s">
+      <c r="I14" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="J14" s="146">
+      <c r="J14" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I14,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>30340</v>
       </c>
-      <c r="K14" s="146">
+      <c r="K14" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I14,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>17260</v>
       </c>
-      <c r="M14" s="142">
+      <c r="M14" s="76">
         <v>2023</v>
       </c>
-      <c r="N14" s="144">
+      <c r="N14" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,"Nickel Products",[1]DATA_TABLE!B2:B265,M14)</f>
         <v>20980</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="142">
+      <c r="A15" s="76">
         <v>2024</v>
       </c>
-      <c r="B15" s="143">
+      <c r="B15" s="77">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Export",[1]DATA_TABLE!B2:B265,A15)</f>
         <v>74390</v>
       </c>
-      <c r="C15" s="144">
+      <c r="C15" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!C2:C265,"Import",[1]DATA_TABLE!B2:B265,A15)</f>
         <v>53510</v>
       </c>
-      <c r="E15" s="145" t="s">
+      <c r="E15" s="79" t="s">
         <v>198</v>
       </c>
-      <c r="F15" s="146">
+      <c r="F15" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E15,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>5458</v>
       </c>
-      <c r="G15" s="146">
+      <c r="G15" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E15,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>0</v>
       </c>
-      <c r="I15" s="145" t="s">
+      <c r="I15" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="J15" s="146">
+      <c r="J15" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I15,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>7908</v>
       </c>
-      <c r="K15" s="146">
+      <c r="K15" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I15,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>16140</v>
       </c>
-      <c r="M15" s="142">
+      <c r="M15" s="76">
         <v>2024</v>
       </c>
-      <c r="N15" s="144">
+      <c r="N15" s="78">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,"Nickel Products",[1]DATA_TABLE!B2:B265,M15)</f>
         <v>22990</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E16" s="145" t="s">
+      <c r="E16" s="79" t="s">
         <v>219</v>
       </c>
-      <c r="F16" s="146">
+      <c r="F16" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E16,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>0</v>
       </c>
-      <c r="G16" s="146">
+      <c r="G16" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E16,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>71260</v>
       </c>
-      <c r="I16" s="145" t="s">
+      <c r="I16" s="79" t="s">
         <v>78</v>
       </c>
-      <c r="J16" s="146">
+      <c r="J16" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I16,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>16356</v>
       </c>
-      <c r="K16" s="146">
+      <c r="K16" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I16,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="5:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E17" s="145" t="s">
+      <c r="E17" s="79" t="s">
         <v>252</v>
       </c>
-      <c r="F17" s="146">
+      <c r="F17" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E17,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>0</v>
       </c>
-      <c r="G17" s="146">
+      <c r="G17" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E17,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>84900</v>
       </c>
-      <c r="I17" s="145" t="s">
+      <c r="I17" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="J17" s="146">
+      <c r="J17" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I17,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>6090</v>
       </c>
-      <c r="K17" s="146">
+      <c r="K17" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I17,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>11640</v>
       </c>
     </row>
     <row r="18" spans="5:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E18" s="145" t="s">
+      <c r="E18" s="79" t="s">
         <v>285</v>
       </c>
-      <c r="F18" s="146">
+      <c r="F18" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E18,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>0</v>
       </c>
-      <c r="G18" s="146">
+      <c r="G18" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E18,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>43220</v>
       </c>
-      <c r="I18" s="145" t="s">
+      <c r="I18" s="79" t="s">
         <v>266</v>
       </c>
-      <c r="J18" s="146">
+      <c r="J18" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I18,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>0</v>
       </c>
-      <c r="K18" s="146">
+      <c r="K18" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I18,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>16780</v>
       </c>
     </row>
     <row r="19" spans="5:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="145" t="s">
+      <c r="E19" s="79" t="s">
         <v>306</v>
       </c>
-      <c r="F19" s="146">
+      <c r="F19" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E19,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>0</v>
       </c>
-      <c r="G19" s="146">
+      <c r="G19" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E19,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>35040</v>
       </c>
-      <c r="I19" s="145" t="s">
+      <c r="I19" s="79" t="s">
         <v>328</v>
       </c>
-      <c r="J19" s="146">
+      <c r="J19" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I19,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>0</v>
       </c>
-      <c r="K19" s="146">
+      <c r="K19" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!F2:F265,I19,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>7150</v>
       </c>
     </row>
     <row r="20" spans="5:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E20" s="145" t="s">
+      <c r="E20" s="79" t="s">
         <v>326</v>
       </c>
-      <c r="F20" s="146">
+      <c r="F20" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E20,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>0</v>
       </c>
-      <c r="G20" s="146">
+      <c r="G20" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E20,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>14170</v>
       </c>
     </row>
     <row r="21" spans="5:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E21" s="145" t="s">
+      <c r="E21" s="79" t="s">
         <v>350</v>
       </c>
-      <c r="F21" s="146">
+      <c r="F21" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E21,[1]DATA_TABLE!C2:C265,"Export")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="146">
+      <c r="G21" s="80">
         <f>SUMIFS([1]DATA_TABLE!H2:H265,[1]DATA_TABLE!D2:D265,E21,[1]DATA_TABLE!C2:C265,"Import")</f>
         <v>24480</v>
       </c>
@@ -20748,6 +20743,21 @@
     <row r="57" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="I8:K8"/>
@@ -20757,21 +20767,6 @@
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="M6:O6"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -20801,85 +20796,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="117" t="s">
+        <v>553</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+    </row>
+    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="118" t="s">
         <v>369</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-    </row>
-    <row r="2" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="108" t="s">
         <v>370</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
-        <v>371</v>
-      </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
     </row>
     <row r="5" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="L5" s="5" t="s">
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="119" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="119"/>
+      <c r="C6" s="120" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="95" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="96" t="s">
-        <v>379</v>
-      </c>
-      <c r="D6" s="96"/>
+      <c r="D6" s="120"/>
       <c r="E6" s="19">
         <f>COUNTA('RAW DATA'!A4:A267)</f>
         <v>264</v>
@@ -20890,25 +20885,25 @@
       <c r="G6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="96" t="s">
+      <c r="H6" s="120" t="s">
+        <v>379</v>
+      </c>
+      <c r="I6" s="120"/>
+      <c r="J6" s="120"/>
+      <c r="K6" s="120"/>
+      <c r="L6" s="19" t="s">
         <v>380</v>
       </c>
-      <c r="I6" s="96"/>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="19" t="s">
+    </row>
+    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="121" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="121"/>
+      <c r="C7" s="122" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="93" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="93"/>
-      <c r="C7" s="94" t="s">
-        <v>382</v>
-      </c>
-      <c r="D7" s="94"/>
+      <c r="D7" s="122"/>
       <c r="E7" s="21">
         <f>COUNTA('RAW DATA'!B4:B267)</f>
         <v>264</v>
@@ -20919,25 +20914,25 @@
       <c r="G7" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="94" t="s">
+      <c r="H7" s="122" t="s">
+        <v>382</v>
+      </c>
+      <c r="I7" s="122"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="I7" s="94"/>
-      <c r="J7" s="94"/>
-      <c r="K7" s="94"/>
-      <c r="L7" s="21" t="s">
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="119" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="119"/>
+      <c r="C8" s="120" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="95" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="95"/>
-      <c r="C8" s="96" t="s">
-        <v>385</v>
-      </c>
-      <c r="D8" s="96"/>
+      <c r="D8" s="120"/>
       <c r="E8" s="19">
         <f>COUNTA('RAW DATA'!C4:C267)</f>
         <v>264</v>
@@ -20948,25 +20943,25 @@
       <c r="G8" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="96" t="s">
+      <c r="H8" s="120" t="s">
+        <v>385</v>
+      </c>
+      <c r="I8" s="120"/>
+      <c r="J8" s="120"/>
+      <c r="K8" s="120"/>
+      <c r="L8" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="19" t="s">
-        <v>387</v>
-      </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="93" t="s">
+      <c r="A9" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="93"/>
-      <c r="C9" s="94" t="s">
-        <v>385</v>
-      </c>
-      <c r="D9" s="94"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="122" t="s">
+        <v>384</v>
+      </c>
+      <c r="D9" s="122"/>
       <c r="E9" s="21">
         <f>COUNTA('RAW DATA'!D4:D267)</f>
         <v>264</v>
@@ -20977,25 +20972,25 @@
       <c r="G9" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="94" t="s">
+      <c r="H9" s="122" t="s">
+        <v>387</v>
+      </c>
+      <c r="I9" s="122"/>
+      <c r="J9" s="122"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="I9" s="94"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94"/>
-      <c r="L9" s="21" t="s">
+    </row>
+    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="119" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="119"/>
+      <c r="C10" s="120" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="95" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="95"/>
-      <c r="C10" s="96" t="s">
-        <v>390</v>
-      </c>
-      <c r="D10" s="96"/>
+      <c r="D10" s="120"/>
       <c r="E10" s="19">
         <f>COUNTA('RAW DATA'!E4:E267)</f>
         <v>264</v>
@@ -21006,25 +21001,25 @@
       <c r="G10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="96" t="s">
+      <c r="H10" s="120" t="s">
+        <v>390</v>
+      </c>
+      <c r="I10" s="120"/>
+      <c r="J10" s="120"/>
+      <c r="K10" s="120"/>
+      <c r="L10" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="19" t="s">
-        <v>392</v>
-      </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="93" t="s">
+      <c r="A11" s="121" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="93"/>
-      <c r="C11" s="94" t="s">
-        <v>385</v>
-      </c>
-      <c r="D11" s="94"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="122" t="s">
+        <v>384</v>
+      </c>
+      <c r="D11" s="122"/>
       <c r="E11" s="21">
         <f>COUNTA('RAW DATA'!F4:F267)</f>
         <v>264</v>
@@ -21035,25 +21030,25 @@
       <c r="G11" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="94" t="s">
+      <c r="H11" s="122" t="s">
+        <v>392</v>
+      </c>
+      <c r="I11" s="122"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="21" t="s">
         <v>393</v>
       </c>
-      <c r="I11" s="94"/>
-      <c r="J11" s="94"/>
-      <c r="K11" s="94"/>
-      <c r="L11" s="21" t="s">
-        <v>394</v>
-      </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="95"/>
-      <c r="C12" s="96" t="s">
-        <v>385</v>
-      </c>
-      <c r="D12" s="96"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="120" t="s">
+        <v>384</v>
+      </c>
+      <c r="D12" s="120"/>
       <c r="E12" s="19">
         <f>COUNTA('RAW DATA'!G4:G267)</f>
         <v>264</v>
@@ -21064,25 +21059,25 @@
       <c r="G12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="96" t="s">
+      <c r="H12" s="120" t="s">
+        <v>394</v>
+      </c>
+      <c r="I12" s="120"/>
+      <c r="J12" s="120"/>
+      <c r="K12" s="120"/>
+      <c r="L12" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="I12" s="96"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="19" t="s">
+    </row>
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="121" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="121"/>
+      <c r="C13" s="122" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="93" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="93"/>
-      <c r="C13" s="94" t="s">
-        <v>397</v>
-      </c>
-      <c r="D13" s="94"/>
+      <c r="D13" s="122"/>
       <c r="E13" s="21">
         <f>COUNTA('RAW DATA'!H4:H267)</f>
         <v>264</v>
@@ -21091,27 +21086,27 @@
         <v>0</v>
       </c>
       <c r="G13" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="H13" s="122" t="s">
         <v>398</v>
       </c>
-      <c r="H13" s="94" t="s">
+      <c r="I13" s="122"/>
+      <c r="J13" s="122"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="21" t="s">
         <v>399</v>
       </c>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
-      <c r="L13" s="21" t="s">
+    </row>
+    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="119" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="119"/>
+      <c r="C14" s="120" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="95" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="95"/>
-      <c r="C14" s="96" t="s">
-        <v>401</v>
-      </c>
-      <c r="D14" s="96"/>
+      <c r="D14" s="120"/>
       <c r="E14" s="19">
         <f>COUNTA('RAW DATA'!I4:I267)</f>
         <v>264</v>
@@ -21120,27 +21115,27 @@
         <v>0</v>
       </c>
       <c r="G14" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="H14" s="120" t="s">
         <v>398</v>
       </c>
-      <c r="H14" s="96" t="s">
-        <v>399</v>
-      </c>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="96"/>
+      <c r="I14" s="120"/>
+      <c r="J14" s="120"/>
+      <c r="K14" s="120"/>
       <c r="L14" s="19" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="121" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="121"/>
+      <c r="C15" s="122" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="93" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="93"/>
-      <c r="C15" s="94" t="s">
-        <v>403</v>
-      </c>
-      <c r="D15" s="94"/>
+      <c r="D15" s="122"/>
       <c r="E15" s="21">
         <f>COUNTA('RAW DATA'!J4:J267)</f>
         <v>264</v>
@@ -21149,27 +21144,27 @@
         <v>0</v>
       </c>
       <c r="G15" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="H15" s="122" t="s">
         <v>398</v>
       </c>
-      <c r="H15" s="94" t="s">
-        <v>399</v>
-      </c>
-      <c r="I15" s="94"/>
-      <c r="J15" s="94"/>
-      <c r="K15" s="94"/>
+      <c r="I15" s="122"/>
+      <c r="J15" s="122"/>
+      <c r="K15" s="122"/>
       <c r="L15" s="21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="95"/>
-      <c r="C16" s="96" t="s">
-        <v>385</v>
-      </c>
-      <c r="D16" s="96"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="120" t="s">
+        <v>384</v>
+      </c>
+      <c r="D16" s="120"/>
       <c r="E16" s="19">
         <f>COUNTA('RAW DATA'!K4:K267)</f>
         <v>264</v>
@@ -21180,72 +21175,72 @@
       <c r="G16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="96" t="s">
+      <c r="H16" s="120" t="s">
+        <v>404</v>
+      </c>
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="19" t="s">
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="115" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="79" t="s">
-        <v>407</v>
-      </c>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="79"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="79"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="115"/>
+      <c r="L19" s="115"/>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>408</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="D20" s="23" t="s">
         <v>409</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="E20" s="23" t="s">
         <v>410</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="F20" s="23" t="s">
         <v>411</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="G20" s="23" t="s">
         <v>412</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="H20" s="23" t="s">
         <v>413</v>
       </c>
-      <c r="H20" s="23" t="s">
+      <c r="I20" s="23" t="s">
         <v>414</v>
       </c>
-      <c r="I20" s="23" t="s">
+      <c r="J20" s="23" t="s">
         <v>415</v>
       </c>
-      <c r="J20" s="23" t="s">
+      <c r="K20" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="K20" s="23" t="s">
+      <c r="L20" s="23" t="s">
         <v>417</v>
       </c>
-      <c r="L20" s="23" t="s">
+    </row>
+    <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="123" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="90" t="s">
-        <v>419</v>
-      </c>
-      <c r="B21" s="90"/>
+      <c r="B21" s="123"/>
       <c r="C21" s="25">
         <f>MIN('RAW DATA'!H4:H267)</f>
         <v>112</v>
@@ -21279,15 +21274,15 @@
         <v>0.99137100859955196</v>
       </c>
       <c r="K21" s="27" t="s">
+        <v>419</v>
+      </c>
+      <c r="L21" s="28"/>
+    </row>
+    <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="124" t="s">
         <v>420</v>
       </c>
-      <c r="L21" s="28"/>
-    </row>
-    <row r="22" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="91" t="s">
-        <v>421</v>
-      </c>
-      <c r="B22" s="91"/>
+      <c r="B22" s="124"/>
       <c r="C22" s="30">
         <f>MIN('RAW DATA'!I4:I267)</f>
         <v>30</v>
@@ -21321,15 +21316,15 @@
         <v>2.2751635924992724</v>
       </c>
       <c r="K22" s="31" t="s">
+        <v>421</v>
+      </c>
+      <c r="L22" s="32"/>
+    </row>
+    <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="123" t="s">
         <v>422</v>
       </c>
-      <c r="L22" s="32"/>
-    </row>
-    <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="90" t="s">
-        <v>423</v>
-      </c>
-      <c r="B23" s="90"/>
+      <c r="B23" s="123"/>
       <c r="C23" s="33">
         <f>MIN('RAW DATA'!J4:J267)</f>
         <v>65</v>
@@ -21363,51 +21358,51 @@
         <v>1.6179553081513967</v>
       </c>
       <c r="K23" s="27" t="s">
+        <v>423</v>
+      </c>
+      <c r="L23" s="28"/>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="106" t="s">
         <v>424</v>
       </c>
-      <c r="L23" s="28"/>
-    </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="87" t="s">
-        <v>425</v>
-      </c>
-      <c r="B25" s="87"/>
-      <c r="C25" s="87"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="K25" s="87"/>
-      <c r="L25" s="87"/>
+      <c r="B25" s="106"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="106"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="106"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="106"/>
+      <c r="L25" s="106"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
+        <v>425</v>
+      </c>
+      <c r="B26" s="34" t="s">
         <v>426</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="C26" s="34" t="s">
         <v>427</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>428</v>
       </c>
       <c r="D26" s="34"/>
       <c r="E26" s="34" t="s">
         <v>50</v>
       </c>
       <c r="G26" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="H26" s="34" t="s">
+        <v>428</v>
+      </c>
+      <c r="I26" s="34" t="s">
+        <v>429</v>
+      </c>
+      <c r="J26" s="34" t="s">
         <v>427</v>
-      </c>
-      <c r="H26" s="34" t="s">
-        <v>429</v>
-      </c>
-      <c r="I26" s="34" t="s">
-        <v>430</v>
-      </c>
-      <c r="J26" s="34" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21422,10 +21417,10 @@
         <f>COUNTIF('RAW DATA'!C4:C267,"Export")/COUNTA('RAW DATA'!C4:C267)</f>
         <v>0.5</v>
       </c>
-      <c r="E27" s="90" t="s">
+      <c r="E27" s="123" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="90"/>
+      <c r="F27" s="123"/>
       <c r="G27" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E27)</f>
         <v>30</v>
@@ -21455,10 +21450,10 @@
         <f>COUNTIF('RAW DATA'!C4:C267,"Import")/COUNTA('RAW DATA'!C4:C267)</f>
         <v>0.5</v>
       </c>
-      <c r="E28" s="91" t="s">
+      <c r="E28" s="124" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="91"/>
+      <c r="F28" s="124"/>
       <c r="G28" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E28)</f>
         <v>30</v>
@@ -21477,10 +21472,10 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="90" t="s">
+      <c r="E29" s="123" t="s">
         <v>136</v>
       </c>
-      <c r="F29" s="90"/>
+      <c r="F29" s="123"/>
       <c r="G29" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E29)</f>
         <v>18</v>
@@ -21499,10 +21494,10 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E30" s="91" t="s">
+      <c r="E30" s="124" t="s">
         <v>156</v>
       </c>
-      <c r="F30" s="91"/>
+      <c r="F30" s="124"/>
       <c r="G30" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E30)</f>
         <v>18</v>
@@ -21521,10 +21516,10 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E31" s="90" t="s">
+      <c r="E31" s="123" t="s">
         <v>178</v>
       </c>
-      <c r="F31" s="90"/>
+      <c r="F31" s="123"/>
       <c r="G31" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E31)</f>
         <v>18</v>
@@ -21543,10 +21538,10 @@
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E32" s="91" t="s">
+      <c r="E32" s="124" t="s">
         <v>198</v>
       </c>
-      <c r="F32" s="91"/>
+      <c r="F32" s="124"/>
       <c r="G32" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E32)</f>
         <v>18</v>
@@ -21565,10 +21560,10 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E33" s="90" t="s">
+      <c r="E33" s="123" t="s">
         <v>219</v>
       </c>
-      <c r="F33" s="90"/>
+      <c r="F33" s="123"/>
       <c r="G33" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E33)</f>
         <v>30</v>
@@ -21587,10 +21582,10 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E34" s="91" t="s">
+      <c r="E34" s="124" t="s">
         <v>252</v>
       </c>
-      <c r="F34" s="91"/>
+      <c r="F34" s="124"/>
       <c r="G34" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E34)</f>
         <v>30</v>
@@ -21609,10 +21604,10 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E35" s="90" t="s">
+      <c r="E35" s="123" t="s">
         <v>285</v>
       </c>
-      <c r="F35" s="90"/>
+      <c r="F35" s="123"/>
       <c r="G35" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E35)</f>
         <v>18</v>
@@ -21631,10 +21626,10 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E36" s="91" t="s">
+      <c r="E36" s="124" t="s">
         <v>306</v>
       </c>
-      <c r="F36" s="91"/>
+      <c r="F36" s="124"/>
       <c r="G36" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E36)</f>
         <v>18</v>
@@ -21653,10 +21648,10 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E37" s="90" t="s">
+      <c r="E37" s="123" t="s">
         <v>326</v>
       </c>
-      <c r="F37" s="90"/>
+      <c r="F37" s="123"/>
       <c r="G37" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E37)</f>
         <v>18</v>
@@ -21675,10 +21670,10 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E38" s="91" t="s">
+      <c r="E38" s="124" t="s">
         <v>350</v>
       </c>
-      <c r="F38" s="91"/>
+      <c r="F38" s="124"/>
       <c r="G38" s="35">
         <f>COUNTIF('RAW DATA'!D4:D267,E38)</f>
         <v>18</v>
@@ -21697,69 +21692,21 @@
       </c>
     </row>
     <row r="40" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="92" t="s">
-        <v>431</v>
-      </c>
-      <c r="B40" s="92"/>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="92"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
+      <c r="A40" s="147"/>
+      <c r="B40" s="147"/>
+      <c r="C40" s="147"/>
+      <c r="D40" s="147"/>
+      <c r="E40" s="147"/>
+      <c r="F40" s="147"/>
+      <c r="G40" s="147"/>
+      <c r="H40" s="147"/>
+      <c r="I40" s="147"/>
+      <c r="J40" s="147"/>
+      <c r="K40" s="147"/>
+      <c r="L40" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="A40:L40"/>
@@ -21768,6 +21715,52 @@
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -21797,87 +21790,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="117" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+    </row>
+    <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="118" t="s">
+        <v>431</v>
+      </c>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="108" t="s">
         <v>432</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-    </row>
-    <row r="2" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="I4" s="106" t="s">
         <v>433</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-    </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
-        <v>434</v>
-      </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="I4" s="87" t="s">
-        <v>435</v>
-      </c>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="106"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="I5" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="J5" s="34" t="s">
         <v>441</v>
       </c>
-      <c r="I5" s="34" t="s">
-        <v>442</v>
-      </c>
-      <c r="J5" s="34" t="s">
-        <v>443</v>
-      </c>
       <c r="K5" s="34" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L5" s="34" t="s">
         <v>34</v>
@@ -22493,15 +22486,15 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="79" t="s">
-        <v>444</v>
-      </c>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
+      <c r="A20" s="115" t="s">
+        <v>442</v>
+      </c>
+      <c r="B20" s="115"/>
+      <c r="C20" s="115"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
       <c r="I20" s="29" t="s">
         <v>343</v>
       </c>
@@ -22527,22 +22520,22 @@
         <v>50</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C21" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="E21" s="23" t="s">
         <v>445</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="F21" s="23" t="s">
         <v>446</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="G21" s="23" t="s">
         <v>447</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>448</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22920,65 +22913,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="117" t="s">
+        <v>448</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+    </row>
+    <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="118" t="s">
+        <v>449</v>
+      </c>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+      <c r="O2" s="118"/>
+      <c r="P2" s="118"/>
+    </row>
+    <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="108" t="s">
         <v>450</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-    </row>
-    <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="M4" s="126" t="s">
         <v>451</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
-      <c r="P2" s="97"/>
-    </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
-        <v>452</v>
-      </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="M4" s="100" t="s">
-        <v>453</v>
-      </c>
-      <c r="N4" s="100"/>
-      <c r="O4" s="100"/>
-      <c r="P4" s="100"/>
+      <c r="N4" s="126"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="126"/>
     </row>
     <row r="5" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
@@ -23015,14 +23008,14 @@
         <v>185</v>
       </c>
       <c r="L5" s="44" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="M5" s="73" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N5" s="72"/>
       <c r="O5" s="45" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -23074,14 +23067,14 @@
         <v>88270</v>
       </c>
       <c r="M6" s="71" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="N6" s="70"/>
-      <c r="O6" s="99">
+      <c r="O6" s="127">
         <f>IFERROR(SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,"China",'RAW DATA'!C4:C267,"Export")/SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!C4:C267,"Export"),0)</f>
         <v>0.43750230555599473</v>
       </c>
-      <c r="P6" s="99"/>
+      <c r="P6" s="127"/>
     </row>
     <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="39" t="s">
@@ -23132,14 +23125,14 @@
         <v>148610</v>
       </c>
       <c r="M7" s="67" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N7" s="68"/>
-      <c r="O7" s="99">
+      <c r="O7" s="127">
         <f>IFERROR(SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,"China",'RAW DATA'!C4:C267,"Import")/SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!C4:C267,"Import"),0)</f>
         <v>0.37301790749624636</v>
       </c>
-      <c r="P7" s="99"/>
+      <c r="P7" s="127"/>
     </row>
     <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="39" t="s">
@@ -23190,14 +23183,14 @@
         <v>79130</v>
       </c>
       <c r="M8" s="69" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="N8" s="70"/>
-      <c r="O8" s="98">
+      <c r="O8" s="128">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,"China",'RAW DATA'!C4:C267,"Export")</f>
         <v>166040</v>
       </c>
-      <c r="P8" s="98"/>
+      <c r="P8" s="128"/>
     </row>
     <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="39" t="s">
@@ -23248,14 +23241,14 @@
         <v>20330</v>
       </c>
       <c r="M9" s="67" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="N9" s="68"/>
-      <c r="O9" s="98">
+      <c r="O9" s="128">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,"China",'RAW DATA'!C4:C267,"Import")</f>
         <v>101860</v>
       </c>
-      <c r="P9" s="98"/>
+      <c r="P9" s="128"/>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="39" t="s">
@@ -23306,14 +23299,14 @@
         <v>37720</v>
       </c>
       <c r="M10" s="69" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="N10" s="70"/>
-      <c r="O10" s="98">
+      <c r="O10" s="128">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,"China",'RAW DATA'!C4:C267,"Export")-SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,"China",'RAW DATA'!C4:C267,"Import")</f>
         <v>64180</v>
       </c>
-      <c r="P10" s="98"/>
+      <c r="P10" s="128"/>
     </row>
     <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
@@ -23364,17 +23357,17 @@
         <v>5458</v>
       </c>
       <c r="M11" s="67" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="N11" s="68"/>
       <c r="O11" s="64"/>
       <c r="P11" s="64" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B12" s="49">
         <f t="shared" ref="B12:L12" si="1">SUM(B6:B11)</f>
@@ -23421,28 +23414,28 @@
         <v>379518</v>
       </c>
       <c r="M12" s="69" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="N12" s="70"/>
       <c r="O12" s="65" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="P12" s="66"/>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="87" t="s">
-        <v>466</v>
-      </c>
-      <c r="B15" s="87"/>
-      <c r="C15" s="87"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="87"/>
-      <c r="F15" s="87"/>
-      <c r="G15" s="87"/>
-      <c r="H15" s="87"/>
-      <c r="I15" s="87"/>
-      <c r="J15" s="87"/>
-      <c r="K15" s="87"/>
+      <c r="A15" s="106" t="s">
+        <v>464</v>
+      </c>
+      <c r="B15" s="106"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="106"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="106"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="106"/>
     </row>
     <row r="16" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50" t="s">
@@ -23479,7 +23472,7 @@
         <v>336</v>
       </c>
       <c r="L16" s="50" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23778,7 +23771,7 @@
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="53" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B23" s="54">
         <f t="shared" ref="B23:L23" si="3">SUM(B17:B22)</f>
@@ -23827,16 +23820,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O9:P9"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="M4:P4"/>
     <mergeCell ref="O6:P6"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O9:P9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -23859,106 +23852,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="117" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="117"/>
+    </row>
+    <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="118" t="s">
+        <v>466</v>
+      </c>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
+    </row>
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="108" t="s">
         <v>467</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-    </row>
-    <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
-        <v>468</v>
-      </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-    </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
-        <v>469</v>
-      </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="82"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="108"/>
     </row>
     <row r="5" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>480</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="39" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B6" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!C4:C267,"Export",'RAW DATA'!B4:B267,2019)</f>
@@ -24011,7 +24004,7 @@
     </row>
     <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B7" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!C4:C267,"Import",'RAW DATA'!B4:B267,2019)</f>
@@ -24064,7 +24057,7 @@
     </row>
     <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B8" s="59">
         <f t="shared" ref="B8:G8" si="1">B6-B7</f>
@@ -24092,65 +24085,65 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="79" t="s">
-        <v>486</v>
-      </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="79"/>
+      <c r="A11" s="115" t="s">
+        <v>484</v>
+      </c>
+      <c r="B11" s="115"/>
+      <c r="C11" s="115"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
+      <c r="K11" s="115"/>
+      <c r="L11" s="115"/>
+      <c r="M11" s="115"/>
+      <c r="N11" s="115"/>
     </row>
     <row r="12" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
         <v>50</v>
       </c>
       <c r="B12" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="D12" s="23" t="s">
         <v>470</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="E12" s="23" t="s">
         <v>471</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="F12" s="23" t="s">
         <v>472</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="G12" s="23" t="s">
         <v>473</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="H12" s="23" t="s">
         <v>474</v>
       </c>
-      <c r="G12" s="23" t="s">
-        <v>475</v>
-      </c>
-      <c r="H12" s="23" t="s">
-        <v>476</v>
-      </c>
       <c r="I12" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="K12" s="23" t="s">
         <v>471</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="L12" s="23" t="s">
         <v>472</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="M12" s="23" t="s">
         <v>473</v>
       </c>
-      <c r="L12" s="23" t="s">
-        <v>474</v>
-      </c>
-      <c r="M12" s="23" t="s">
-        <v>475</v>
-      </c>
       <c r="N12" s="23" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24206,7 +24199,7 @@
         <v>5.5412371134020644E-2</v>
       </c>
       <c r="N13" s="61" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24262,7 +24255,7 @@
         <v>-0.1269559032716927</v>
       </c>
       <c r="N14" s="61" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24318,7 +24311,7 @@
         <v>9.5805529075309925E-2</v>
       </c>
       <c r="N15" s="61" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24374,7 +24367,7 @@
         <v>0.12307692307692308</v>
       </c>
       <c r="N16" s="61" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24430,7 +24423,7 @@
         <v>-0.16809116809116809</v>
       </c>
       <c r="N17" s="61" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24486,7 +24479,7 @@
         <v>-5.4054054054054057E-2</v>
       </c>
       <c r="N18" s="61" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -24524,93 +24517,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="117" t="s">
+        <v>492</v>
+      </c>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+    </row>
+    <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="118" t="s">
+        <v>493</v>
+      </c>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="108" t="s">
         <v>494</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-    </row>
-    <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
-        <v>495</v>
-      </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
-        <v>496</v>
-      </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="108"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="108"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="108"/>
     </row>
     <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
+        <v>495</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>481</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>482</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>483</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>496</v>
+      </c>
+      <c r="G5" s="44" t="s">
         <v>497</v>
       </c>
-      <c r="C5" s="44" t="s">
-        <v>483</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>484</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>485</v>
-      </c>
-      <c r="F5" s="44" t="s">
+      <c r="H5" s="44" t="s">
         <v>498</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="I5" s="44" t="s">
         <v>499</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="J5" s="44" t="s">
         <v>500</v>
       </c>
-      <c r="I5" s="44" t="s">
+      <c r="K5" s="44" t="s">
         <v>501</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="L5" s="44" t="s">
         <v>502</v>
       </c>
-      <c r="K5" s="44" t="s">
-        <v>503</v>
-      </c>
-      <c r="L5" s="44" t="s">
-        <v>504</v>
-      </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="124" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="91"/>
+      <c r="B6" s="124"/>
       <c r="C6" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A6,'RAW DATA'!C4:C267,"Export")</f>
         <v>166040</v>
@@ -24648,14 +24641,14 @@
         <v>0.90855614973262022</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="123" t="s">
         <v>61</v>
       </c>
-      <c r="B7" s="90"/>
+      <c r="B7" s="123"/>
       <c r="C7" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A7,'RAW DATA'!C4:C267,"Export")</f>
         <v>66950</v>
@@ -24697,10 +24690,10 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="124" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="91"/>
+      <c r="B8" s="124"/>
       <c r="C8" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A8,'RAW DATA'!C4:C267,"Export")</f>
         <v>53254</v>
@@ -24738,14 +24731,14 @@
         <v>0.45993542706193136</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="123" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="90"/>
+      <c r="B9" s="123"/>
       <c r="C9" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A9,'RAW DATA'!C4:C267,"Export")</f>
         <v>7908</v>
@@ -24783,14 +24776,14 @@
         <v>0.11302982731554168</v>
       </c>
       <c r="L9" s="63" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="91" t="s">
+      <c r="A10" s="124" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="91"/>
+      <c r="B10" s="124"/>
       <c r="C10" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A10,'RAW DATA'!C4:C267,"Export")</f>
         <v>10520</v>
@@ -24828,14 +24821,14 @@
         <v>-0.10869565217391308</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="123" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="90"/>
+      <c r="B11" s="123"/>
       <c r="C11" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A11,'RAW DATA'!C4:C267,"Export")</f>
         <v>30340</v>
@@ -24873,14 +24866,14 @@
         <v>0.75595238095238093</v>
       </c>
       <c r="L11" s="63" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="91" t="s">
+      <c r="A12" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="91"/>
+      <c r="B12" s="124"/>
       <c r="C12" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A12,'RAW DATA'!C4:C267,"Export")</f>
         <v>16356</v>
@@ -24918,14 +24911,14 @@
         <v>0.24126455906821964</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="123" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="90"/>
+      <c r="B13" s="123"/>
       <c r="C13" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A13,'RAW DATA'!C4:C267,"Export")</f>
         <v>6090</v>
@@ -24963,14 +24956,14 @@
         <v>0.21739130434782616</v>
       </c>
       <c r="L13" s="63" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="124" t="s">
         <v>266</v>
       </c>
-      <c r="B14" s="91"/>
+      <c r="B14" s="124"/>
       <c r="C14" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A14,'RAW DATA'!C4:C267,"Export")</f>
         <v>0</v>
@@ -25008,14 +25001,14 @@
         <v>0</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="123" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="90"/>
+      <c r="B15" s="123"/>
       <c r="C15" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A15,'RAW DATA'!C4:C267,"Export")</f>
         <v>12260</v>
@@ -25057,10 +25050,10 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="91" t="s">
+      <c r="A16" s="124" t="s">
         <v>129</v>
       </c>
-      <c r="B16" s="91"/>
+      <c r="B16" s="124"/>
       <c r="C16" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A16,'RAW DATA'!C4:C267,"Export")</f>
         <v>9800</v>
@@ -25102,10 +25095,10 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="B17" s="90"/>
+      <c r="B17" s="123"/>
       <c r="C17" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A17,'RAW DATA'!C4:C267,"Export")</f>
         <v>0</v>
@@ -25147,10 +25140,10 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="91" t="s">
+      <c r="A18" s="124" t="s">
         <v>336</v>
       </c>
-      <c r="B18" s="91"/>
+      <c r="B18" s="124"/>
       <c r="C18" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A18,'RAW DATA'!C4:C267,"Export")</f>
         <v>0</v>
@@ -25192,10 +25185,10 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="123" t="s">
         <v>298</v>
       </c>
-      <c r="B19" s="90"/>
+      <c r="B19" s="123"/>
       <c r="C19" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A19,'RAW DATA'!C4:C267,"Export")</f>
         <v>0</v>
@@ -25237,10 +25230,10 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="91" t="s">
+      <c r="A20" s="124" t="s">
         <v>343</v>
       </c>
-      <c r="B20" s="91"/>
+      <c r="B20" s="124"/>
       <c r="C20" s="55">
         <f>SUMIFS('RAW DATA'!H4:H267,'RAW DATA'!F4:F267,A20,'RAW DATA'!C4:C267,"Export")</f>
         <v>0</v>
@@ -25282,10 +25275,10 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="101" t="s">
-        <v>512</v>
-      </c>
-      <c r="B21" s="101"/>
+      <c r="A21" s="129" t="s">
+        <v>510</v>
+      </c>
+      <c r="B21" s="129"/>
       <c r="C21" s="54">
         <f>SUM(C6:C20)</f>
         <v>379518</v>
@@ -25300,43 +25293,43 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="92" t="s">
-        <v>513</v>
-      </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="92"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
+      <c r="A23" s="125" t="s">
+        <v>511</v>
+      </c>
+      <c r="B23" s="125"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A23:L23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -25358,304 +25351,281 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="130" t="s">
+        <v>512</v>
+      </c>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+    </row>
+    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="118"/>
+      <c r="B2" s="118"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+    </row>
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="131" t="s">
+        <v>513</v>
+      </c>
+      <c r="B4" s="131"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="131"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+    </row>
+    <row r="5" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="132" t="s">
         <v>514</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-    </row>
-    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
+      <c r="B5" s="132"/>
+      <c r="C5" s="120" t="s">
         <v>515</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-    </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="117" t="s">
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="120"/>
+      <c r="I5" s="120"/>
+      <c r="J5" s="120"/>
+    </row>
+    <row r="6" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="133" t="s">
         <v>516</v>
       </c>
-      <c r="B4" s="117"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-    </row>
-    <row r="5" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="118" t="s">
+      <c r="B6" s="133"/>
+      <c r="C6" s="112" t="s">
         <v>517</v>
       </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="96" t="s">
+      <c r="D6" s="112"/>
+      <c r="E6" s="112"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="112"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="112"/>
+      <c r="J6" s="112"/>
+    </row>
+    <row r="7" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="134" t="s">
         <v>518</v>
       </c>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="96"/>
-    </row>
-    <row r="6" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="113" t="s">
+      <c r="B7" s="134"/>
+      <c r="C7" s="114" t="s">
         <v>519</v>
       </c>
-      <c r="B6" s="113"/>
-      <c r="C6" s="81" t="s">
+      <c r="D7" s="114"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="114"/>
+      <c r="J7" s="114"/>
+    </row>
+    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="135" t="s">
         <v>520</v>
       </c>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-    </row>
-    <row r="7" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="114" t="s">
+      <c r="B13" s="135"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+    </row>
+    <row r="14" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="136" t="s">
+        <v>514</v>
+      </c>
+      <c r="B14" s="136"/>
+      <c r="C14" s="120" t="s">
         <v>521</v>
       </c>
-      <c r="B7" s="114"/>
-      <c r="C7" s="76" t="s">
+      <c r="D14" s="120"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="120"/>
+      <c r="J14" s="120"/>
+    </row>
+    <row r="15" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="137" t="s">
+        <v>516</v>
+      </c>
+      <c r="B15" s="137"/>
+      <c r="C15" s="112" t="s">
         <v>522</v>
       </c>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="76"/>
-      <c r="J7" s="76"/>
-    </row>
-    <row r="13" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="115" t="s">
+      <c r="D15" s="112"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="112"/>
+    </row>
+    <row r="16" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="138" t="s">
+        <v>518</v>
+      </c>
+      <c r="B16" s="138"/>
+      <c r="C16" s="114" t="s">
         <v>523</v>
       </c>
-      <c r="B13" s="115"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="115"/>
-    </row>
-    <row r="14" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="110" t="s">
-        <v>517</v>
-      </c>
-      <c r="B14" s="110"/>
-      <c r="C14" s="96" t="s">
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="114"/>
+    </row>
+    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="139" t="s">
         <v>524</v>
       </c>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-    </row>
-    <row r="15" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="111" t="s">
-        <v>519</v>
-      </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="81" t="s">
+      <c r="B22" s="139"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="139"/>
+      <c r="F22" s="139"/>
+      <c r="G22" s="139"/>
+      <c r="H22" s="139"/>
+      <c r="I22" s="139"/>
+      <c r="J22" s="139"/>
+    </row>
+    <row r="23" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="140" t="s">
+        <v>514</v>
+      </c>
+      <c r="B23" s="140"/>
+      <c r="C23" s="120" t="s">
         <v>525</v>
       </c>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-    </row>
-    <row r="16" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="112" t="s">
-        <v>521</v>
-      </c>
-      <c r="B16" s="112"/>
-      <c r="C16" s="76" t="s">
+      <c r="D23" s="120"/>
+      <c r="E23" s="120"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="120"/>
+      <c r="J23" s="120"/>
+    </row>
+    <row r="24" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="141" t="s">
+        <v>516</v>
+      </c>
+      <c r="B24" s="141"/>
+      <c r="C24" s="112" t="s">
         <v>526</v>
       </c>
-      <c r="D16" s="76"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="76"/>
-      <c r="H16" s="76"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="76"/>
-    </row>
-    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="107" t="s">
+      <c r="D24" s="112"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="112"/>
+    </row>
+    <row r="25" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="144" t="s">
+        <v>518</v>
+      </c>
+      <c r="B25" s="144"/>
+      <c r="C25" s="114" t="s">
         <v>527</v>
       </c>
-      <c r="B22" s="107"/>
-      <c r="C22" s="107"/>
-      <c r="D22" s="107"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="107"/>
-      <c r="H22" s="107"/>
-      <c r="I22" s="107"/>
-      <c r="J22" s="107"/>
-    </row>
-    <row r="23" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="108" t="s">
-        <v>517</v>
-      </c>
-      <c r="B23" s="108"/>
-      <c r="C23" s="96" t="s">
+      <c r="D25" s="114"/>
+      <c r="E25" s="114"/>
+      <c r="F25" s="114"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="114"/>
+      <c r="I25" s="114"/>
+      <c r="J25" s="114"/>
+    </row>
+    <row r="31" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="145" t="s">
         <v>528</v>
       </c>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96"/>
-    </row>
-    <row r="24" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="109" t="s">
-        <v>519</v>
-      </c>
-      <c r="B24" s="109"/>
-      <c r="C24" s="81" t="s">
+      <c r="B31" s="145"/>
+      <c r="C31" s="145"/>
+      <c r="D31" s="145"/>
+      <c r="E31" s="145"/>
+      <c r="F31" s="145"/>
+      <c r="G31" s="145"/>
+      <c r="H31" s="145"/>
+      <c r="I31" s="145"/>
+      <c r="J31" s="145"/>
+    </row>
+    <row r="32" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="146" t="s">
+        <v>514</v>
+      </c>
+      <c r="B32" s="146"/>
+      <c r="C32" s="120" t="s">
         <v>529</v>
       </c>
-      <c r="D24" s="81"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="81"/>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="81"/>
-    </row>
-    <row r="25" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="104" t="s">
-        <v>521</v>
-      </c>
-      <c r="B25" s="104"/>
-      <c r="C25" s="76" t="s">
+      <c r="D32" s="120"/>
+      <c r="E32" s="120"/>
+      <c r="F32" s="120"/>
+      <c r="G32" s="120"/>
+      <c r="H32" s="120"/>
+      <c r="I32" s="120"/>
+      <c r="J32" s="120"/>
+    </row>
+    <row r="33" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="142" t="s">
+        <v>516</v>
+      </c>
+      <c r="B33" s="142"/>
+      <c r="C33" s="112" t="s">
         <v>530</v>
       </c>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-    </row>
-    <row r="31" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="105" t="s">
+      <c r="D33" s="112"/>
+      <c r="E33" s="112"/>
+      <c r="F33" s="112"/>
+      <c r="G33" s="112"/>
+      <c r="H33" s="112"/>
+      <c r="I33" s="112"/>
+      <c r="J33" s="112"/>
+    </row>
+    <row r="34" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="143" t="s">
+        <v>518</v>
+      </c>
+      <c r="B34" s="143"/>
+      <c r="C34" s="114" t="s">
         <v>531</v>
       </c>
-      <c r="B31" s="105"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="105"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="105"/>
-      <c r="J31" s="105"/>
-    </row>
-    <row r="32" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="106" t="s">
-        <v>517</v>
-      </c>
-      <c r="B32" s="106"/>
-      <c r="C32" s="96" t="s">
-        <v>532</v>
-      </c>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="96"/>
-    </row>
-    <row r="33" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="102" t="s">
-        <v>519</v>
-      </c>
-      <c r="B33" s="102"/>
-      <c r="C33" s="81" t="s">
-        <v>533</v>
-      </c>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="81"/>
-    </row>
-    <row r="34" spans="1:10" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="103" t="s">
-        <v>521</v>
-      </c>
-      <c r="B34" s="103"/>
-      <c r="C34" s="76" t="s">
-        <v>534</v>
-      </c>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
+      <c r="D34" s="114"/>
+      <c r="E34" s="114"/>
+      <c r="F34" s="114"/>
+      <c r="G34" s="114"/>
+      <c r="H34" s="114"/>
+      <c r="I34" s="114"/>
+      <c r="J34" s="114"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:J6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:J7"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:J23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:J24"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="C33:J33"/>
     <mergeCell ref="A34:B34"/>
@@ -25665,6 +25635,27 @@
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="C32:J32"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:J23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:J24"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:J15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:J6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:J7"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:J5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -25693,34 +25684,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="89" t="s">
-        <v>535</v>
-      </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
+      <c r="A2" s="97" t="s">
+        <v>532</v>
+      </c>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
